--- a/artfynd/A 60667-2024 artfynd.xlsx
+++ b/artfynd/A 60667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121798430</v>
+        <v>121796883</v>
       </c>
       <c r="B2" t="n">
-        <v>98113</v>
+        <v>105218</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,54 +687,54 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Bottorp NNV 410 m, Ög</t>
+          <t>Bottorp N 645 m, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550901</v>
+        <v>550930</v>
       </c>
       <c r="R2" t="n">
-        <v>6513204</v>
+        <v>6513452</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121796883</v>
+        <v>121798430</v>
       </c>
       <c r="B3" t="n">
-        <v>105218</v>
+        <v>98113</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,54 +811,54 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>130</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bottorp N 645 m, Ög</t>
+          <t>Bottorp NNV 410 m, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550930</v>
+        <v>550901</v>
       </c>
       <c r="R3" t="n">
-        <v>6513452</v>
+        <v>6513204</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
